--- a/reports/tuned_model_metrics.xlsx
+++ b/reports/tuned_model_metrics.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.995164825341299</v>
+        <v>1.995164825341298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5963603444410407</v>
+        <v>0.5963603444410406</v>
       </c>
       <c r="D2" t="n">
-        <v>3.185745408664587</v>
+        <v>3.185745408664586</v>
       </c>
       <c r="E2" t="n">
-        <v>1.149355908553005</v>
+        <v>1.149355908553004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.808528880805941</v>
+        <v>0.8085288808059412</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06954960687913218</v>
+        <v>0.06954960687913207</v>
       </c>
       <c r="H2" t="n">
         <v>1.735028434816812</v>
@@ -507,7 +507,7 @@
         <v>0.4372873840297378</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1451</v>
+        <v>0.3033</v>
       </c>
     </row>
   </sheetData>
